--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
   <si>
     <t>ID</t>
   </si>
@@ -209,7 +209,7 @@
     <t>2024-07-25 00:00:00.0</t>
   </si>
   <si>
-    <t>2025-03-24 00:00:00.0</t>
+    <t>2025-05-24 00:00:00.0</t>
   </si>
   <si>
     <t>100016</t>
@@ -221,7 +221,7 @@
     <t>2024-09-24 00:00:00.0</t>
   </si>
   <si>
-    <t>2025-04-29 00:00:00.0</t>
+    <t>2025-06-29 00:00:00.0</t>
   </si>
   <si>
     <t>100017</t>
@@ -233,7 +233,7 @@
     <t>2024-10-29 00:00:00.0</t>
   </si>
   <si>
-    <t>2025-05-30 00:00:00.0</t>
+    <t>2025-07-30 00:00:00.0</t>
   </si>
   <si>
     <t>100018</t>
@@ -245,7 +245,7 @@
     <t>2024-12-02 00:00:00.0</t>
   </si>
   <si>
-    <t>2025-06-18 00:00:00.0</t>
+    <t>2025-08-18 00:00:00.0</t>
   </si>
   <si>
     <t>100019</t>
@@ -257,7 +257,7 @@
     <t>2024-12-18 00:00:00.0</t>
   </si>
   <si>
-    <t>2025-07-28 00:00:00.0</t>
+    <t>2025-09-28 00:00:00.0</t>
   </si>
   <si>
     <t>100020</t>
@@ -267,6 +267,18 @@
   </si>
   <si>
     <t>2025-01-28 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-10-25 00:00:00.0</t>
+  </si>
+  <si>
+    <t>100021</t>
+  </si>
+  <si>
+    <t>1.38.x</t>
+  </si>
+  <si>
+    <t>2025-02-25 00:00:00.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -328,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -712,6 +724,23 @@
         <v>82</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -221,7 +221,7 @@
     <t>2024-09-24 00:00:00.0</t>
   </si>
   <si>
-    <t>2025-06-29 00:00:00.0</t>
+    <t>2025-09-30 00:00:00.0</t>
   </si>
   <si>
     <t>100017</t>
@@ -291,6 +291,18 @@
   </si>
   <si>
     <t>2025-03-27 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-01-26 18:59:04.0</t>
+  </si>
+  <si>
+    <t>100023</t>
+  </si>
+  <si>
+    <t>1.41.x</t>
+  </si>
+  <si>
+    <t>2025-05-26 00:00:00.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -352,7 +364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -770,6 +782,23 @@
         <v>90</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -339,6 +339,18 @@
   </si>
   <si>
     <t>2025-09-26 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-06-28 18:04:39.0</t>
+  </si>
+  <si>
+    <t>100027</t>
+  </si>
+  <si>
+    <t>1.46.x</t>
+  </si>
+  <si>
+    <t>2025-10-28 00:00:00.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -400,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -886,6 +898,23 @@
         <v>106</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
